--- a/solution/report/1조_세미_팀프로젝트_기획설계.xlsx
+++ b/solution/report/1조_세미_팀프로젝트_기획설계.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.기본정보" sheetId="1" r:id="R3ff607fd23ba478f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.요구사항정의서개요" sheetId="2" r:id="Rebd40d7ac0d14204"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.기능요구사항상세" sheetId="3" r:id="R1c4e18687cb34889"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.업무분담" sheetId="4" r:id="Re20c720bb76044e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.테이블구조(DB)" sheetId="5" r:id="R0917253fdbcb4826"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.네이밍규칙" sheetId="6" r:id="R002ef2708f03482b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.디렉토리구조" sheetId="7" r:id="R30e096c30bb94ad6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.패키지구조" sheetId="8" r:id="Rbda223894fc44bdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.개발서비스환경" sheetId="9" r:id="R260565158c0a4782"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.실무예시데이터" sheetId="10" r:id="Rae4ebdda3a5b4cf9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11.SQL스크립트" sheetId="11" r:id="Rf1f621735af1419f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12.테스트케이스" sheetId="12" r:id="Rb115c96ac966489e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1.기본정보" sheetId="1" r:id="Rb5e51daf75e14af8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.요구사항정의서개요" sheetId="2" r:id="Rfb57d8fc10a74f57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.기능요구사항상세" sheetId="3" r:id="R0e9a6d718a094585"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4.업무분담" sheetId="4" r:id="R29ceb1c4115a4c28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.테이블구조(DB)" sheetId="5" r:id="Rc4e5ac55c6874b56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.네이밍규칙" sheetId="6" r:id="R6936c258ecdc4327"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.디렉토리구조" sheetId="7" r:id="R5b0c4ae6380140f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.패키지구조" sheetId="8" r:id="R6a3b5d5580bd4d36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.개발서비스환경" sheetId="9" r:id="Rf81f373824a24159"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.실무예시데이터" sheetId="10" r:id="Rbf40c6327b754b59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11.SQL스크립트" sheetId="11" r:id="R8d4450f3a7ba45ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12.테스트케이스" sheetId="12" r:id="R7540e25991ae4c68"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3852,10 +3852,10 @@
         <x:v>박서현</x:v>
       </x:c>
       <x:c r="F6" s="413" t="str">
-        <x:v>2026-10-15</x:v>
+        <x:v>2026-10-25</x:v>
       </x:c>
       <x:c r="G6" s="415" t="str">
-        <x:v>v2.2</x:v>
+        <x:v>v2.3</x:v>
       </x:c>
       <x:c r="H6"/>
     </x:row>
@@ -4169,21 +4169,15 @@
           <x:t xml:space="preserve">4단계 — 마무리·발표</x:t>
         </x:is>
       </x:c>
-      <x:c r="B23" s="128" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">10/19 ~ 10/26</x:t>
-        </x:is>
+      <x:c r="B23" s="128" t="str">
+        <x:v>10/19 ~ 10/25</x:v>
       </x:c>
       <x:c r="C23" s="380" t="n"/>
-      <x:c r="D23" s="137" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">8일</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E23" s="229" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">오류 수정, 결과보고서·시연자료 최종화, 10/26 발표</x:t>
-        </x:is>
+      <x:c r="D23" s="137" t="str">
+        <x:v>7일</x:v>
+      </x:c>
+      <x:c r="E23" s="229" t="str">
+        <x:v>오류 수정, 결과보고서·시연자료 최종화, 10/26 발표 준비</x:v>
       </x:c>
       <x:c r="F23" s="373" t="n"/>
       <x:c r="G23" s="373" t="n"/>
@@ -5596,10 +5590,8 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="331" customFormat="1" ht="35.099998474121094" customHeight="1">
-      <x:c r="A1" s="393" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">12. 테스트 케이스 (2026-10-07 기준)</x:t>
-        </x:is>
+      <x:c r="A1" s="393" t="str">
+        <x:v>12. 테스트 케이스 (2026-10-25 기준)</x:v>
       </x:c>
       <x:c r="B1" s="381" t="n"/>
       <x:c r="C1" s="381" t="n"/>
@@ -5610,10 +5602,8 @@
       <x:c r="H1" s="79" t="n"/>
     </x:row>
     <x:row r="2" s="331" customFormat="1" ht="18" customHeight="1">
-      <x:c r="A2" s="394" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">※ 소스 기준 기본 테스트 기록과 발표 전 재검증 항목을 구분함</x:t>
-        </x:is>
+      <x:c r="A2" s="394" t="str">
+        <x:v>※ 로컬 주요 기능·Tomcat·DB·REST API·Slack Webhook 동작 확인 완료. 개별 예외·실패 경로와 실제 배포 환경 검증 상태는 각 항목에 별도 표시함.</x:v>
       </x:c>
       <x:c r="B2" s="395" t="n"/>
       <x:c r="C2" s="395" t="n"/>
